--- a/output/2026-09-15_21_Croazia_Brodsko-posavska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-15_21_Croazia_Brodsko-posavska_Depolverazione_Trattamento_aria.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore/rappresentante macchinari industriali: compressori CompAir, pompe a vuoto e soffianti Elmo Rietschle, Robuschi, Nash. Dati di contatto confermati su fonti terze indipendenti (Fininfo/Companywall). Non specialista puro di dust collection ma settore tecnologicamente adiacente (vuoto/aria industriale).</t>
+          <t>Distributore/rappresentante macchinari industriali: compressori CompAir, pompe a vuoto e soffianti Elmo Rietschle, Robuschi, Nash. Dati di contatto confermati su fonti terze indipendenti (Fininfo/Companywall). Non specialista puro di dust collection ma settore tecnologicamente adiacente (vuoto/aria industriale). [DUPLICATO — vedi anche: 2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/output/2026-09-15_21_Croazia_Brodsko-posavska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-15_21_Croazia_Brodsko-posavska_Depolverazione_Trattamento_aria.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-15_21_Croazia_Brodsko-posavska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-15_21_Croazia_Brodsko-posavska_Depolverazione_Trattamento_aria.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Catena retail nazionale, apertura filiale locale confermata (settembre 2024, Tome Skalice 6). Categoria dedicata 'Industrijski usisavaci' con marchio Karcher, linea industriale di aspirazione/depolverazione confermata dal produttore. Canale generalista elettronica/elettrodomestici, non specialista B2B industriale: valutare se il volume/target e adatto per Dupuy.</t>
+          <t>Catena retail nazionale, apertura filiale locale confermata (settembre 2024, Tome Skalice 6). Categoria dedicata 'Industrijski usisavaci' con marchio Karcher, linea industriale di aspirazione/depolverazione confermata dal produttore. Canale generalista elettronica/elettrodomestici, non specialista B2B industriale: valutare se il volume/target e adatto per Dupuy. [DUPLICATO — vedi anche: 2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
